--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,30 +444,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>zararliLat</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>phi</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>doz</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>mrl</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>grup</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>gecerlilik</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>aciklama</t>
         </is>
@@ -501,30 +506,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Haplothrips tritici</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>25 ml/da</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -558,30 +568,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Haplothrips tritici</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>25 ml/da</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -615,30 +630,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Haplothrips tritici</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>25 ml/da</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -672,30 +692,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Haplothrips tritici</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>25 ml/da</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -729,30 +754,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Mycosphaerella nawae</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>70 gün</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Fitotoksisite riski bulunmaktadır, dormant dönemde kullanılmalıdır.Bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidir.</t>
         </is>
@@ -786,30 +816,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Phragmidium mucronatum</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>100 ml/ 100 l su</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -843,30 +878,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -900,30 +940,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0,005</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -957,30 +1002,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1014,30 +1064,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1071,30 +1126,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>0,01*</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1128,30 +1188,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1185,30 +1250,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>0,06</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1242,30 +1312,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>0,007</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1299,30 +1374,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>0,06</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1356,30 +1436,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>40 ml/da</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0,3</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1413,30 +1498,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Botrytis cinerea</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>80 g/100 l su</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1470,30 +1560,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>0.3 mg/kg</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1527,30 +1622,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>60 ml/da</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>0.3 mg/kg</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1584,30 +1684,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>0.05* mg/kg</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1641,30 +1746,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>35 gün</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>0.3 mg/kg</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1698,30 +1808,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Diplocarpon rosae</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>100 ml/ 100 l su</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1755,30 +1870,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>7 Gün</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>20 ml/100 L su</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1812,30 +1932,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>14 Gün</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>50 ml/100 L su</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1869,30 +1994,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Peronospora arborescens</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>35 gün</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>40-105 ml/da</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>0.5 mg/kg</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1926,30 +2056,35 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Plutella xylostella = Plutella maculipennis</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>100 ml/da</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1983,30 +2118,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>21 gün</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>70 ml/da</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2040,30 +2180,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>1500 ml/100 L su</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>MRL uygulanmaz.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2097,30 +2242,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>Agriotes spp.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
@@ -2154,30 +2304,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>5 mg/kg</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
@@ -2211,30 +2366,35 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2268,30 +2428,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2325,30 +2490,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>10 mg / kg</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2382,30 +2552,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2439,30 +2614,35 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2496,30 +2676,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2553,30 +2738,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2610,30 +2800,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2667,30 +2862,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2724,30 +2924,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2781,30 +2986,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>50 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>3 mg/kg</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2838,30 +3048,35 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Plasmopara spp, Bremia lactucae</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>15 mg / kg</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2895,30 +3110,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Plasmopara spp, Bremia lactucae</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>10 mg/kg</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2952,30 +3172,35 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Plasmopara spp, Bremia lactucae</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3009,30 +3234,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Plasmopara spp, Bremia lactucae</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3066,30 +3296,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Plasmopara spp, Bremia lactucae</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>10 mg/kg</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3123,30 +3358,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>10 mg/kg</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3180,30 +3420,35 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>10 mg/kg</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3237,30 +3482,35 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3294,30 +3544,35 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>15 mg/kg</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3351,30 +3606,35 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3408,30 +3668,35 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>10 mg / kg</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3465,30 +3730,35 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>15 mg/kg</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3522,30 +3792,35 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>10 mg/kg</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3579,30 +3854,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>(Peronospora belbahrii)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>70 mg / kg</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3636,30 +3916,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>45 ml / da</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>15 mg / kg</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3693,30 +3978,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>45 ml / da</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>15 mg / kg</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3750,30 +4040,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>45 ml / da</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>70 mg / kg</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3807,30 +4102,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>14 gün</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>70 mg/kg</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3864,30 +4164,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>10 mg / kg</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3921,30 +4226,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>70 mg / kg</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3978,30 +4288,35 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>15 mg / kg</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4035,30 +4350,35 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>45 ml/da</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>15 mg / kg</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4092,30 +4412,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>Spodoptera littoralis</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
           <t>7 Gün</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>15 ml/da</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>0.6 mg/kg</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Fitotoksisite riski bulunmaktadır, dormant dönemde kullanılmalıdır.Bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,32 +791,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -826,74 +826,74 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,59 +903,59 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,24 +965,24 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,24 +1089,24 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1116,32 +1116,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,69 +1213,69 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1287,57 +1287,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1473,57 +1473,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1535,57 +1535,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1597,57 +1597,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1659,52 +1659,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1721,52 +1721,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1783,57 +1783,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,007</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,12 +1845,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,32 +1860,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1907,47 +1907,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1984,32 +1984,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2031,57 +2031,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,57 +2093,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,57 +2155,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2217,171 +2217,171 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2403,57 +2403,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2465,57 +2465,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2527,57 +2527,57 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2589,57 +2589,57 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2651,84 +2651,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2738,22 +2738,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,44 +2763,44 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2810,22 +2810,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2837,32 +2837,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,22 +2872,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,47 +3147,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,47 +3209,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,17 +3534,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,32 +3906,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,17 +4154,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,32 +4216,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,27 +4340,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4387,60 +4387,494 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SEMİZOTU</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>45 ml / da</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15 mg / kg</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DEREOTU</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>45 ml / da</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>70 mg / kg</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NANE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>70 mg/kg</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MARUL</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>KÜLLEME</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10 mg / kg</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>FESLEĞEN</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>KÜLLEME</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>70 mg / kg</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ISPANAK</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>KÜLLEME</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>15 mg / kg</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SEMİZOTU</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>KÜLLEME</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>15 mg / kg</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>KARATE ZEON</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>ISPANAK</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>Spodoptera littoralis</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>7 Gün</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>15 ml/da</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>0.6 mg/kg</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,54 +474,69 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>verilisTarihi</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>iller</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>aciklama</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>bku_id</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,59 +546,72 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>4356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,19 +621,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>4358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,37 +656,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,13 +696,26 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Antalya, Diyarbakır, İstanbul, Kocaeli, Muğla, Rize, Sakarya, Trabzon</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>4370</v>
       </c>
     </row>
     <row r="5">
@@ -682,7 +736,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +761,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -722,116 +776,142 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>4294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,59 +921,72 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,19 +996,32 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4296</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -925,12 +1031,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -945,17 +1051,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -970,8 +1076,21 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>4354</v>
       </c>
     </row>
     <row r="10">
@@ -992,7 +1111,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1032,8 +1151,21 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
+      </c>
+      <c r="O10" t="n">
+        <v>4355</v>
       </c>
     </row>
     <row r="11">
@@ -1054,7 +1186,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1069,17 +1201,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1094,19 +1226,32 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
+      </c>
+      <c r="O11" t="n">
+        <v>4357</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1116,7 +1261,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1131,17 +1276,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1156,194 +1301,246 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Antalya, Diyarbakır, İstanbul, Kocaeli, Muğla, Rize, Sakarya, Trabzon</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>4368</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
-        </is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4306</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>4112</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>4100</v>
       </c>
     </row>
     <row r="16">
@@ -1364,7 +1561,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1586,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1404,8 +1601,21 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>4102</v>
       </c>
     </row>
     <row r="17">
@@ -1426,7 +1636,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1661,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1466,8 +1676,21 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>4104</v>
       </c>
     </row>
     <row r="18">
@@ -1488,7 +1711,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1736,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1528,8 +1751,21 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>4106</v>
       </c>
     </row>
     <row r="19">
@@ -1550,7 +1786,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1590,8 +1826,21 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>4108</v>
       </c>
     </row>
     <row r="20">
@@ -1612,7 +1861,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1886,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1652,8 +1901,21 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>4110</v>
       </c>
     </row>
     <row r="21">
@@ -1674,7 +1936,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1961,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,007</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1714,8 +1976,21 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>4092</v>
       </c>
     </row>
     <row r="22">
@@ -1736,7 +2011,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +2036,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1776,8 +2051,21 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>4094</v>
       </c>
     </row>
     <row r="23">
@@ -1798,7 +2086,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +2111,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1838,132 +2126,171 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>4098</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>4061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>4062</v>
       </c>
     </row>
     <row r="26">
@@ -1984,27 +2311,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2019,44 +2346,57 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>4082</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2066,12 +2406,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2081,59 +2421,72 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>4081</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,19 +2496,32 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>4091</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2165,37 +2531,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2205,29 +2571,42 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>4097</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2237,12 +2616,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2631,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2272,8 +2651,21 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>4083</v>
       </c>
     </row>
     <row r="31">
@@ -2334,59 +2726,72 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>4239</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,59 +2801,72 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>4063</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2458,8 +2876,21 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>4238</v>
       </c>
     </row>
     <row r="34">
@@ -2520,54 +2951,67 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>4076</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2577,59 +3021,72 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>3844</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,137 +3096,176 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>4078</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
-        </is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Aydın</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>3840</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
-        </is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>3819</v>
       </c>
     </row>
     <row r="39">
@@ -2830,8 +3326,21 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>3806</v>
       </c>
     </row>
     <row r="40">
@@ -2892,8 +3401,21 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>3807</v>
       </c>
     </row>
     <row r="41">
@@ -2954,8 +3476,21 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>3940</v>
       </c>
     </row>
     <row r="42">
@@ -3016,8 +3551,21 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>3956</v>
       </c>
     </row>
     <row r="43">
@@ -3078,8 +3626,21 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>3962</v>
       </c>
     </row>
     <row r="44">
@@ -3140,8 +3701,21 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>3966</v>
       </c>
     </row>
     <row r="45">
@@ -3202,8 +3776,21 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>3970</v>
       </c>
     </row>
     <row r="46">
@@ -3264,8 +3851,21 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>3974</v>
       </c>
     </row>
     <row r="47">
@@ -3291,12 +3891,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3326,8 +3926,21 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>4058</v>
       </c>
     </row>
     <row r="48">
@@ -3348,7 +3961,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,7 +3976,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3373,7 +3986,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,8 +4001,21 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>4059</v>
       </c>
     </row>
     <row r="49">
@@ -3410,22 +4036,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3435,7 +4061,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,8 +4076,21 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>4060</v>
       </c>
     </row>
     <row r="50">
@@ -3472,17 +4111,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3492,12 +4131,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3512,8 +4151,21 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>4052</v>
       </c>
     </row>
     <row r="51">
@@ -3534,17 +4186,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,12 +4206,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3574,8 +4226,21 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>4053</v>
       </c>
     </row>
     <row r="52">
@@ -3596,22 +4261,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3621,7 +4286,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3636,8 +4301,21 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>4055</v>
       </c>
     </row>
     <row r="53">
@@ -3658,17 +4336,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3683,7 +4361,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3698,8 +4376,21 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>4056</v>
       </c>
     </row>
     <row r="54">
@@ -3720,17 +4411,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3740,12 +4431,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3760,8 +4451,21 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>4057</v>
       </c>
     </row>
     <row r="55">
@@ -3782,22 +4486,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3807,7 +4511,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3822,8 +4526,21 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>4010</v>
       </c>
     </row>
     <row r="56">
@@ -3849,17 +4566,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3869,7 +4586,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3884,8 +4601,21 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>4011</v>
       </c>
     </row>
     <row r="57">
@@ -3906,32 +4636,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3946,8 +4676,21 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>4035</v>
       </c>
     </row>
     <row r="58">
@@ -3968,17 +4711,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3988,12 +4731,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4008,8 +4751,21 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>4038</v>
       </c>
     </row>
     <row r="59">
@@ -4030,17 +4786,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4070,59 +4826,72 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>4040</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,8 +4901,21 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>İzmir ve Manisa</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>3770</v>
       </c>
     </row>
     <row r="61">
@@ -4154,22 +4936,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4179,7 +4961,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4194,8 +4976,21 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>3991</v>
       </c>
     </row>
     <row r="62">
@@ -4216,17 +5011,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4236,7 +5031,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4256,8 +5051,21 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>3992</v>
       </c>
     </row>
     <row r="63">
@@ -4278,22 +5086,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4303,7 +5111,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4318,8 +5126,21 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>3993</v>
       </c>
     </row>
     <row r="64">
@@ -4340,17 +5161,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4360,12 +5181,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4380,8 +5201,21 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>3994</v>
       </c>
     </row>
     <row r="65">
@@ -4402,17 +5236,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4422,12 +5256,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4442,8 +5276,21 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>3995</v>
       </c>
     </row>
     <row r="66">
@@ -4464,17 +5311,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,12 +5331,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,8 +5351,21 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>3996</v>
       </c>
     </row>
     <row r="67">
@@ -4526,17 +5386,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4566,8 +5426,21 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>3997</v>
       </c>
     </row>
     <row r="68">
@@ -4588,22 +5461,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4613,7 +5486,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4628,8 +5501,21 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>3998</v>
       </c>
     </row>
     <row r="69">
@@ -4650,22 +5536,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4675,7 +5561,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4690,8 +5576,21 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>3999</v>
       </c>
     </row>
     <row r="70">
@@ -4752,8 +5651,21 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="71">
@@ -4814,24 +5726,37 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>4009</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,32 +5766,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4876,8 +5801,21 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
-        </is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Tum Turkiye</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>3775</v>
       </c>
     </row>
   </sheetData>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,22 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>verilisTarihi</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>iller</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
           <t>aciklama</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>bku_id</t>
         </is>
       </c>
     </row>
@@ -551,21 +536,8 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
-      </c>
-      <c r="O2" t="n">
-        <v>4356</v>
       </c>
     </row>
     <row r="3">
@@ -626,21 +598,8 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
-      </c>
-      <c r="O3" t="n">
-        <v>4358</v>
       </c>
     </row>
     <row r="4">
@@ -701,21 +660,8 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Antalya, Diyarbakır, İstanbul, Kocaeli, Muğla, Rize, Sakarya, Trabzon</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
           <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
-      </c>
-      <c r="O4" t="n">
-        <v>4370</v>
       </c>
     </row>
     <row r="5">
@@ -776,21 +722,8 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>4293</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -851,21 +784,8 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>4294</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -926,21 +846,8 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>4295</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1001,21 +908,8 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>4296</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1076,21 +970,8 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
-      </c>
-      <c r="O9" t="n">
-        <v>4354</v>
       </c>
     </row>
     <row r="10">
@@ -1151,21 +1032,8 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
-      </c>
-      <c r="O10" t="n">
-        <v>4355</v>
       </c>
     </row>
     <row r="11">
@@ -1226,21 +1094,8 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Muğla, Kocaeli, İstanbul, Trabzon, Sakarya, Antalya, Diyarbakır, Rize</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
           <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
-      </c>
-      <c r="O11" t="n">
-        <v>4357</v>
       </c>
     </row>
     <row r="12">
@@ -1301,21 +1156,8 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Antalya, Diyarbakır, İstanbul, Kocaeli, Muğla, Rize, Sakarya, Trabzon</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
           <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
-      </c>
-      <c r="O12" t="n">
-        <v>4368</v>
       </c>
     </row>
     <row r="13">
@@ -1376,21 +1218,8 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>4306</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1451,21 +1280,8 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>4112</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1526,21 +1342,8 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>4100</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1601,21 +1404,8 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>4102</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1676,21 +1466,8 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>4104</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1751,21 +1528,8 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>4106</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1826,21 +1590,8 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>4108</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1901,21 +1652,8 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>4110</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1976,21 +1714,8 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>4092</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2051,21 +1776,8 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>4094</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2126,21 +1838,8 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>4098</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2201,21 +1900,8 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>4061</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2276,21 +1962,8 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>4062</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2351,21 +2024,8 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>4082</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2426,21 +2086,8 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>4081</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2501,21 +2148,8 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>4091</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2576,21 +2210,8 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>4097</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2651,21 +2272,8 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>4083</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2726,21 +2334,8 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>4239</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2801,21 +2396,8 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>4063</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2876,21 +2458,8 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>4238</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2951,21 +2520,8 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>4076</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3026,21 +2582,8 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>3844</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3101,21 +2644,8 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>4078</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3176,21 +2706,8 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Aydın</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
           <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
-      </c>
-      <c r="O37" t="n">
-        <v>3840</v>
       </c>
     </row>
     <row r="38">
@@ -3251,21 +2768,8 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Afyonkarahisar</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
-      </c>
-      <c r="O38" t="n">
-        <v>3819</v>
       </c>
     </row>
     <row r="39">
@@ -3326,21 +2830,8 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>3806</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -3401,21 +2892,8 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>3807</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -3476,21 +2954,8 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>3940</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3551,21 +3016,8 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>3956</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3626,21 +3078,8 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>3962</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3701,21 +3140,8 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>3966</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -3776,21 +3202,8 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>3970</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -3851,21 +3264,8 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>3974</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3926,21 +3326,8 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>4058</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4001,21 +3388,8 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>4059</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4076,21 +3450,8 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>4060</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4151,21 +3512,8 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>4052</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -4226,21 +3574,8 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>4053</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -4301,21 +3636,8 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>4055</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4376,21 +3698,8 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O53" t="n">
-        <v>4056</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -4451,21 +3760,8 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O54" t="n">
-        <v>4057</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4526,21 +3822,8 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O55" t="n">
-        <v>4010</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -4601,21 +3884,8 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>4011</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -4676,21 +3946,8 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O57" t="n">
-        <v>4035</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -4751,21 +4008,8 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O58" t="n">
-        <v>4038</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4826,21 +4070,8 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O59" t="n">
-        <v>4040</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4901,21 +4132,8 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>İzmir ve Manisa</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
           <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
         </is>
-      </c>
-      <c r="O60" t="n">
-        <v>3770</v>
       </c>
     </row>
     <row r="61">
@@ -4976,21 +4194,8 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O61" t="n">
-        <v>3991</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -5051,21 +4256,8 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" t="n">
-        <v>3992</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -5126,21 +4318,8 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O63" t="n">
-        <v>3993</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -5201,21 +4380,8 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" t="n">
-        <v>3994</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -5276,21 +4442,8 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O65" t="n">
-        <v>3995</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -5351,21 +4504,8 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O66" t="n">
-        <v>3996</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -5426,21 +4566,8 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O67" t="n">
-        <v>3997</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -5501,21 +4628,8 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O68" t="n">
-        <v>3998</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -5576,21 +4690,8 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O69" t="n">
-        <v>3999</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -5651,21 +4752,8 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O70" t="n">
-        <v>4008</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -5726,21 +4814,8 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O71" t="n">
-        <v>4009</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -5801,21 +4876,8 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Tum Turkiye</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O72" t="n">
-        <v>3775</v>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,19 +593,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,37 +615,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -739,37 +739,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -779,59 +779,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,59 +841,59 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -1225,57 +1225,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1287,57 +1287,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1349,57 +1349,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1845,57 +1845,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,007</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1907,57 +1907,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1969,52 +1969,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2031,47 +2031,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,47 +2093,47 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2165,37 +2165,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2279,17 +2279,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2341,52 +2341,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2418,32 +2418,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2465,57 +2465,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,136 +2639,136 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,32 +3906,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,17 +4030,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4077,52 +4077,52 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,17 +4340,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4402,17 +4402,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,17 +4464,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4526,17 +4526,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4573,52 +4573,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4650,22 +4650,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,47 +543,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -605,47 +605,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,69 +655,69 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -729,32 +729,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -779,59 +779,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,59 +841,59 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -930,32 +930,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -992,32 +992,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1027,54 +1027,54 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,34 +1084,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1163,218 +1163,218 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1384,39 +1384,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1426,32 +1426,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1523,69 +1523,69 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2031,57 +2031,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,007</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,52 +2093,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2155,52 +2155,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2279,57 +2279,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2341,57 +2341,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2403,57 +2403,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2527,57 +2527,57 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2589,42 +2589,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2639,59 +2639,59 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2713,119 +2713,119 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2899,32 +2899,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,22 +2934,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2961,84 +2961,84 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3073,44 +3073,44 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3120,22 +3120,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3147,32 +3147,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3182,1699 +3182,25 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>APRIN XL 350 ES</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>350 g/l Metalaxyl-m</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Toprak kökenli patojenler</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>50 ml/100 kg tohum</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3 mg/kg</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>MARUL</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10 mg / kg</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>DEREOTU</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SEMİZOTU</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15 mg/kg</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ROKA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10 mg/kg</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ROKA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Mildiyö</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10 mg/kg</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SEMİZOTU</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Mildiyö</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15 mg / kg</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TERE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Mildiyö</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10 mg/kg</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>MAYDANOZ</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Mildiyö</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>DEREOTU</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Mildiyö</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>MARUL</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>10 mg / kg</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TERE</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10 mg/kg</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ROKA</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10 mg/kg</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DEREOTU</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SEMİZOTU</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>15 mg/kg</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>MİLDİYÖ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>(Peronospora belbahrii)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>70 mg / kg</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ISPANAK</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>45 ml / da</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15 mg / kg</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>SEMİZOTU</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>45 ml / da</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15 mg / kg</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>DEREOTU</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>45 ml / da</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>70 mg / kg</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NANE</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>KARATE ZEON</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>ISPANAK</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Pamuk yaprakkurdu</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Spodoptera littoralis</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>7 Gün</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>15 ml/da</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>0.6 mg/kg</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>İzmir ve Manisa illeri için geçici kullanım izni verilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>70 mg / kg</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>ISPANAK</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>15 mg / kg</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>SEMİZOTU</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>15 mg / kg</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MARUL</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10 mg / kg</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,57 +543,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -605,114 +605,114 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -729,47 +729,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -784,54 +784,54 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,69 +841,69 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,69 +965,69 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1101,156 +1101,156 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1260,121 +1260,121 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1384,158 +1384,158 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1545,22 +1545,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1597,57 +1597,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1659,57 +1659,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1721,57 +1721,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1783,57 +1783,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,57 +1845,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1907,57 +1907,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1969,12 +1969,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1984,32 +1984,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0,007</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,12 +2093,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,12 +2155,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2217,47 +2217,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2279,322 +2279,322 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2604,32 +2604,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,59 +2639,59 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2701,69 +2701,69 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2775,57 +2775,57 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2899,47 +2899,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2961,42 +2961,42 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3011,121 +3011,121 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3147,60 +3147,1238 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>KAVUN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Danaburnu</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>40 ml/da</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DOMATES</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Danaburnu</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>40 ml/da</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KARPUZ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Danaburnu</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>40 ml/da</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PATLICAN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Danaburnu</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gryllotalpa gryllotalpa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>40 ml/da</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SWITCH 62.5 WG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GÜL (Süs bitkisi)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kurşuni küf</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Botrytis cinerea</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>80 g/100 l su</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ANASON</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Anason yaprak lekesi</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Cercospora malkoffii</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>66 ml/100 kg tohuma</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.3 mg/kg</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ANASON</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Anason yaprak lekesi</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Cercospora malkoffii</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>60 ml/da</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.3 mg/kg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>KİMYON</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Alternaria yaprak lekesi</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>35 gün</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.3 mg/kg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CELEST MAX 100 FS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>100 g/l Fludioxonil</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>KİMYON</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kök çürüklüğü hastalığı</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>10 ml/100 kg tohuma</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.05* mg/kg</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QUADRİS MAXX</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GÜL (Süs bitkisi)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Gülde karaleke</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Diplocarpon rosae</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>100 ml/ 100 l su</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NİNJA 5 EC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AVOKADO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>İncir Teke Böceği</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7 Gün</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>20 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AMPLİGO 150 ZC</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AVOKADO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>İncir Teke Böceği</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>14 Gün</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>50 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NİNJA 5 EC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Lahana yaprakgüvesi</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Plutella xylostella = Plutella maculipennis</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>100 ml/da</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAŞHAŞ </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Haşhaş mildiyösü</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Peronospora arborescens</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>35 gün</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>40-105 ml/da</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>PLOCAFİR</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>FORTENZA 600 FS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>600 g/l Cyantraniliprole</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PATATES</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Telkurtları</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Agriotes spp.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>28 gün</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>22.5 ml/100 kg tohum</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ENGİNAR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Toprak kökenli patojenler</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Turunçgil unlubiti</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Planococcus citri</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1000 ml/100 l su</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>YABAN MERSİNİ</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Turunçgil unlubiti</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Planococcus citri</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,57 +729,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -791,47 +791,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -898,17 +898,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -960,79 +960,79 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1597,47 +1597,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1659,17 +1659,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1721,47 +1721,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,17 +1798,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,32 +1860,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1969,57 +1969,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2031,57 +2031,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,57 +2093,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,57 +2155,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2217,47 +2217,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2279,156 +2279,156 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,59 +2438,59 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,270 +2500,270 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2775,12 +2775,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2837,12 +2837,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2852,32 +2852,32 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2899,12 +2899,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2961,57 +2961,57 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3073,59 +3073,59 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3135,59 +3135,59 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,24 +3197,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3224,32 +3224,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,24 +3321,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,121 +3383,121 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3519,57 +3519,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3581,52 +3581,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3643,52 +3643,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3705,57 +3705,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,12 +3767,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3782,32 +3782,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,47 +3829,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3891,12 +3891,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3953,57 +3953,57 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4030,17 +4030,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,47 +4077,47 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,62 +4139,62 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4216,32 +4216,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4251,44 +4251,44 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4298,22 +4298,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4325,60 +4325,804 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>KİMYON</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Alternaria yaprak lekesi</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Alternaria spp.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>35 gün</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.3 mg/kg</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CELEST MAX 100 FS</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>100 g/l Fludioxonil</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>KİMYON</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Kök çürüklüğü hastalığı</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>10 ml/100 kg tohuma</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.05* mg/kg</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QUADRİS MAXX</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GÜL (Süs bitkisi)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Gülde karaleke</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Diplocarpon rosae</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>14 gün</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>100 ml/ 100 l su</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AMPLİGO 150 ZC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AVOKADO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>İncir Teke Böceği</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>14 Gün</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>50 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NİNJA 5 EC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AVOKADO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>İncir Teke Böceği</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>7 Gün</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>20 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NİNJA 5 EC</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Lahana yaprakgüvesi</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Plutella xylostella = Plutella maculipennis</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>100 ml/da</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAŞHAŞ </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Haşhaş mildiyösü</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Peronospora arborescens</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>35 gün</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>40-105 ml/da</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>0.5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>PLOCAFİR</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>FORTENZA 600 FS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>600 g/l Cyantraniliprole</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PATATES</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Telkurtları</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Agriotes spp.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>28 gün</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>22.5 ml/100 kg tohum</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ENGİNAR</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Toprak kökenli patojenler</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Turunçgil unlubiti</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Planococcus citri</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1000 ml/100 l su</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>YABAN MERSİNİ</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Turunçgil unlubiti</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Planococcus citri</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -543,62 +543,62 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -620,22 +620,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,32 +744,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -791,32 +791,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -826,22 +826,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -853,114 +853,114 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -977,62 +977,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1240,32 +1240,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1302,32 +1302,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,22 +1364,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,22 +1488,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1736,17 +1736,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2031,47 +2031,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2093,17 +2093,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2155,32 +2155,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2190,17 +2190,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2217,32 +2217,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,84 +2252,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2403,47 +2403,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2465,47 +2465,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2527,47 +2527,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2651,47 +2651,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2713,47 +2713,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,59 +2763,59 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,69 +2825,69 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2949,91 +2949,91 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,22 +3085,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,14 +3140,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3157,37 +3157,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3224,32 +3224,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3348,32 +3348,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,29 +3383,29 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3457,47 +3457,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3519,57 +3519,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3581,57 +3581,57 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4139,57 +4139,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4340,27 +4340,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4387,17 +4387,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4407,27 +4407,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4449,17 +4449,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4573,52 +4573,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4697,52 +4697,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4759,109 +4759,109 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,47 +4883,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,74 +4933,74 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4325,114 +4325,114 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4449,47 +4449,47 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4511,57 +4511,57 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4573,52 +4573,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4650,32 +4650,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4712,32 +4712,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4774,32 +4774,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4809,121 +4809,121 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,47 +4945,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4995,59 +4995,59 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -5084,45 +5084,107 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Turunçgil unlubiti</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Planococcus citri</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1000 ml/100 l su</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>YABAN MERSİNİ</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Turunçgil unlubiti</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Planococcus citri</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2341,47 +2341,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2391,59 +2391,59 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2453,59 +2453,59 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2713,171 +2713,171 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2899,62 +2899,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,19 +3140,19 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3162,32 +3162,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,7 +3395,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,37 +3405,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,44 +3445,44 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3492,59 +3492,59 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,146 +3554,146 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3705,52 +3705,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3767,57 +3767,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,57 +3829,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4263,57 +4263,57 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,27 +4464,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4511,47 +4511,47 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4573,47 +4573,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4623,24 +4623,24 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4650,32 +4650,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4697,57 +4697,57 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4759,52 +4759,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4821,74 +4821,74 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,109 +5007,109 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5146,45 +5146,231 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FORTENZA 600 FS</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>600 g/l Cyantraniliprole</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PATATES</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Telkurtları</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Agriotes spp.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>28 gün</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>22.5 ml/100 kg tohum</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Turunçgil unlubiti</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Planococcus citri</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1000 ml/100 l su</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>YABAN MERSİNİ</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Turunçgil unlubiti</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Planococcus citri</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,42 +481,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -531,54 +531,54 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -593,245 +593,245 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -853,47 +853,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -977,47 +977,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1039,47 +1039,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,47 +1101,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,32 +1163,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1198,22 +1198,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1275,59 +1275,59 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1337,59 +1337,59 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1399,64 +1399,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1473,114 +1473,114 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1597,62 +1597,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -1674,17 +1674,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1736,32 +1736,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2155,52 +2155,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2217,119 +2217,119 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2341,47 +2341,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2391,34 +2391,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2433,17 +2433,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2453,59 +2453,59 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2515,59 +2515,59 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2651,47 +2651,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2713,47 +2713,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2775,47 +2775,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2914,32 +2914,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2961,32 +2961,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,59 +2996,59 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3058,208 +3058,208 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3348,32 +3348,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3410,32 +3410,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,29 +3445,29 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3519,47 +3519,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3569,59 +3569,59 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,69 +3631,69 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3705,57 +3705,57 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,94 +3767,94 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3864,74 +3864,74 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3941,69 +3941,69 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4015,52 +4015,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4077,57 +4077,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,57 +4139,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4449,57 +4449,57 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4511,57 +4511,57 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4697,52 +4697,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4759,57 +4759,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,57 +4821,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,12 +4883,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,69 +4933,69 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5022,32 +5022,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,59 +5057,59 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5131,47 +5131,47 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5193,47 +5193,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5243,69 +5243,69 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5317,60 +5317,370 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ENGİNAR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Toprak kökenli patojenler</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>PLOCAFİR</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>EW</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FORTENZA 600 FS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>600 g/l Cyantraniliprole</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>PATATES</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Telkurtları</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Agriotes spp.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>28 gün</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>22.5 ml/100 kg tohum</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0,15</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Turunçgil unlubiti</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Planococcus citri</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1000 ml/100 l su</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>YABAN MERSİNİ</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Turunçgil unlubiti</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Planococcus citri</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>1000 ml/100 l su</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,42 +481,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -791,94 +791,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -915,32 +915,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -950,74 +950,74 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1039,47 +1039,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,47 +1101,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,32 +1163,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1198,22 +1198,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1275,59 +1275,59 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1337,59 +1337,59 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1399,64 +1399,64 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1473,114 +1473,114 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1597,62 +1597,62 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1674,17 +1674,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,32 +1984,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,32 +2294,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2527,52 +2527,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2589,119 +2589,119 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2713,47 +2713,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,59 +2763,59 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,34 +2825,34 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2862,22 +2862,22 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,29 +2887,29 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2961,17 +2961,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,47 +3147,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,47 +3209,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3271,69 +3271,69 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3457,12 +3457,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3534,32 +3534,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3569,24 +3569,24 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3777,37 +3777,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3817,59 +3817,59 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3953,109 +3953,109 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,57 +4077,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,57 +4139,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4759,32 +4759,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4831,37 +4831,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,119 +4883,119 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5022,27 +5022,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5069,57 +5069,57 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5161,17 +5161,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5193,57 +5193,57 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,57 +5255,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5317,171 +5317,171 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,47 +5503,47 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5553,59 +5553,59 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5615,74 +5615,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>YABAN MERSİNİ</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Turunçgil unlubiti</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Planococcus citri</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1000 ml/100 l su</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -3333,7 +3333,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3574,19 +3574,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3829,7 +3829,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3839,37 +3839,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4077,52 +4077,52 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4139,57 +4139,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4635,57 +4635,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4697,57 +4697,57 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4759,52 +4759,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,64 +4814,64 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,57 +4883,57 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,57 +5007,57 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5193,52 +5193,52 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5317,52 +5317,52 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -853,47 +853,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -915,52 +915,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,54 +970,54 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1027,59 +1027,59 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,59 +1089,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1349,47 +1349,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1473,52 +1473,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1535,114 +1535,114 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1659,62 +1659,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,32 +1860,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2527,52 +2527,52 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2589,119 +2589,119 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2713,47 +2713,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,59 +2763,59 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,59 +2825,59 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2887,59 +2887,59 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2961,47 +2961,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,47 +3147,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,47 +3209,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3829,22 +3829,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3953,22 +3953,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4008,54 +4008,54 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,47 +4077,47 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,57 +4139,57 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4511,57 +4511,57 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4573,57 +4573,57 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4635,119 +4635,119 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,57 +5007,57 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -853,47 +853,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -915,52 +915,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -970,54 +970,54 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1027,59 +1027,59 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,59 +1089,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1349,47 +1349,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1411,17 +1411,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1431,27 +1431,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1473,52 +1473,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1535,114 +1535,114 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1659,62 +1659,62 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,32 +1860,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2527,32 +2527,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,59 +2639,59 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,59 +2763,59 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2899,47 +2899,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2961,47 +2961,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,52 +3147,52 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3209,62 +3209,62 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3574,19 +3574,19 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3829,47 +3829,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3953,22 +3953,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4008,54 +4008,54 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,57 +4077,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,64 +4504,64 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4573,57 +4573,57 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4759,52 +4759,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4821,57 +4821,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,57 +4883,57 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,7 +4945,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4955,37 +4955,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5017,37 +5017,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5193,52 +5193,52 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5317,52 +5317,52 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,27 +496,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -526,12 +526,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -558,27 +558,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -588,59 +588,59 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -853,42 +853,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -903,54 +903,54 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -965,44 +965,44 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1012,22 +1012,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,47 +1039,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,59 +1089,59 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1151,59 +1151,59 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,59 +1213,59 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1349,47 +1349,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1411,47 +1411,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1473,47 +1473,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1535,47 +1535,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1597,52 +1597,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1659,176 +1659,176 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,32 +1984,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,32 +2232,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2527,32 +2527,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,59 +2639,59 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2763,59 +2763,59 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2899,17 +2899,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2961,47 +2961,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,52 +3147,52 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3209,62 +3209,62 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3333,124 +3333,124 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3581,12 +3581,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3636,19 +3636,19 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3658,32 +3658,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3891,47 +3891,47 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4008,39 +4008,39 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4050,74 +4050,74 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,69 +4127,69 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,52 +4201,52 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4263,57 +4263,57 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4325,57 +4325,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4759,32 +4759,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4831,37 +4831,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,119 +4883,119 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,57 +5007,57 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5069,52 +5069,52 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5131,47 +5131,47 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,47 +5255,47 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5379,119 +5379,119 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,122 +5503,246 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>FORTENZA 600 FS</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>PATATES</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Telkurtları</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Agriotes spp.</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ARPA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,24 +3631,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3658,32 +3658,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t xml:space="preserve">BUĞDAY </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Buğdaygil tripsleri</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Haplothrips tritici</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>25 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>ÇAVDAR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>YULAF</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,32 +3844,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3906,32 +3906,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4077,22 +4077,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4132,54 +4132,54 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,47 +4201,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4263,57 +4263,57 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4325,57 +4325,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4573,57 +4573,57 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4635,57 +4635,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4752,64 +4752,64 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,57 +4821,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5069,57 +5069,57 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5131,57 +5131,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5332,32 +5332,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5379,57 +5379,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,52 +5441,52 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5503,124 +5503,124 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ENGİNAR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>5 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,27 +496,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -543,52 +543,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -605,47 +605,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -682,27 +682,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -744,27 +744,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -806,27 +806,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -841,74 +841,74 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -930,27 +930,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -960,74 +960,74 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,69 +1039,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1111,59 +1111,59 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1173,270 +1173,270 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1446,59 +1446,59 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1508,17 +1508,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1535,47 +1535,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1597,52 +1597,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1659,176 +1659,176 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,32 +2170,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,22 +2232,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2852,22 +2852,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2914,17 +2914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,17 +3085,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3105,27 +3105,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,17 +3147,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3167,27 +3167,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,47 +3209,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,47 +3271,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,47 +3333,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,47 +3395,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3457,37 +3457,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,255 +3507,255 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ARPA</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BUĞDAY </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ÇAVDAR</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,47 +3767,47 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>YULAF</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Buğdaygil tripsleri</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Haplothrips tritici</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>25 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3817,74 +3817,74 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3953,22 +3953,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4015,17 +4015,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4077,17 +4077,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4139,171 +4139,171 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4313,64 +4313,64 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4387,57 +4387,57 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4449,52 +4449,52 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4573,57 +4573,57 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4635,57 +4635,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5069,57 +5069,57 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5131,69 +5131,69 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5203,37 +5203,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,57 +5255,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5317,57 +5317,57 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5394,32 +5394,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,17 +5441,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5503,57 +5503,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,109 +5565,109 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ENGİNAR</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pythium spp., Rhizoctonia spp., Sclerotium spp.</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Aydın ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,60 +5689,184 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>FORTENZA 600 FS</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>PATATES</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Telkurtları</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Agriotes spp.</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2051,17 +2051,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,27 +2108,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2232,22 +2232,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2609,22 +2609,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3043,17 +3043,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3457,57 +3457,57 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3519,52 +3519,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3705,7 +3705,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3715,52 +3715,52 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3812,141 +3812,141 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4015,12 +4015,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4070,19 +4070,19 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4132,29 +4132,29 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4263,22 +4263,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4318,39 +4318,39 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4360,74 +4360,74 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4449,47 +4449,47 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5203,37 +5203,37 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5327,37 +5327,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5441,57 +5441,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,52 +5503,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5565,57 +5565,57 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5642,32 +5642,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,32 +5704,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5751,47 +5751,47 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5813,60 +5813,122 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>FORTENZA 600 FS</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>PATATES</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Telkurtları</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Agriotes spp.</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,52 +543,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,47 +615,47 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -667,57 +667,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -774,126 +774,126 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCORE 250 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>250 g/l Difenoconazole</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10 ml / 100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -930,27 +930,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1039,42 +1039,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1101,42 +1101,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1411,42 +1411,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
@@ -1535,47 +1535,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,17 +1674,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1845,47 +1845,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,17 +1922,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2217,47 +2217,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,17 +2790,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2914,17 +2914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3038,17 +3038,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,47 +3147,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3271,47 +3271,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,47 +3333,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,47 +3395,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3457,32 +3457,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3812,34 +3812,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3891,57 +3891,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,17 +3983,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4015,12 +4015,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4070,29 +4070,29 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4169,17 +4169,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4263,22 +4263,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4387,47 +4387,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4449,17 +4449,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4635,57 +4635,57 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5208,27 +5208,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,7 +5255,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,37 +5265,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5317,47 +5317,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5394,27 +5394,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,47 +5441,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,47 +5503,47 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5553,64 +5553,64 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5627,47 +5627,47 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5704,32 +5704,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5751,57 +5751,57 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5813,47 +5813,47 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Yaprakbiti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Brevicoryne brassicae</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>70 ml/da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,60 +5875,122 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>FORTENZA 600 FS</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>PATATES</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Telkurtları</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>Agriotes spp.</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,47 +543,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SCORE 250 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>250 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,34 +640,34 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10 ml / 100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -729,32 +729,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -779,59 +779,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -853,57 +853,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -977,52 +977,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1101,32 +1101,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1151,54 +1151,54 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1270,59 +1270,59 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1473,42 +1473,42 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1523,188 +1523,188 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1721,47 +1721,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1845,17 +1845,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1865,27 +1865,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2031,47 +2031,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2217,47 +2217,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,32 +2294,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2403,47 +2403,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2604,32 +2604,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2728,22 +2728,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,47 +2837,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,47 +3085,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3162,22 +3162,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,47 +3209,47 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,47 +3271,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,17 +3395,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3457,52 +3457,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3519,32 +3519,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,22 +3554,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3581,47 +3581,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,19 +3631,19 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3653,104 +3653,104 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3777,42 +3777,42 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,59 +3822,59 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,39 +3884,39 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3926,74 +3926,74 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4003,59 +4003,59 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,59 +4065,59 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4169,17 +4169,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4201,22 +4201,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4263,22 +4263,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4293,17 +4293,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4318,14 +4318,14 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4380,178 +4380,178 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,69 +4561,69 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4821,57 +4821,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5193,57 +5193,57 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,57 +5255,57 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5317,52 +5317,52 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5394,27 +5394,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,47 +5441,47 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,52 +5503,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,64 +5558,64 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5627,57 +5627,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,12 +5689,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5739,64 +5739,64 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5813,47 +5813,47 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,47 +5875,47 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5937,60 +5937,246 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HAŞHAŞ </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Haşhaş mildiyösü</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Peronospora arborescens</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>35 gün</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>40-105 ml/da</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0.5 mg/kg</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KARATE ZEON</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>KANOLA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Yaprakbiti</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Brevicoryne brassicae</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>21 gün</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>70 ml/da</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0,2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PLOCAFİR</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>700 g/l Mineral Yağ</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ERİK</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ERİK KOŞNİLİ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sphaerolecanium prunastri</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1500 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>MRL uygulanmaz.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>FORTENZA 600 FS</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>FS</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>PATATES</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Telkurtları</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Agriotes spp.</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>28 gün</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5999,47 +5999,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yaprakbiti</t>
+          <t>ERİK KOŞNİLİ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brevicoryne brassicae</t>
+          <t>Sphaerolecanium prunastri</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>70 ml/da</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>MRL uygulanmaz.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6061,47 +6061,47 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6111,72 +6111,10 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>FORTENZA 600 FS</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>600 g/l Cyantraniliprole</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>PATATES</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Telkurtları</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Agriotes spp.</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>28 gün</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>22.5 ml/100 kg tohum</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1659,32 +1659,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1709,44 +1709,44 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1756,44 +1756,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2051,27 +2051,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2093,17 +2093,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2403,17 +2403,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2423,27 +2423,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2465,47 +2465,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,27 +2790,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2857,22 +2857,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2914,22 +2914,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3023,17 +3023,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,27 +3043,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,17 +3085,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3105,27 +3105,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3271,17 +3271,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3291,27 +3291,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,47 +3333,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,17 +3395,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3457,17 +3457,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3643,52 +3643,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3705,47 +3705,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,7 +3767,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3777,104 +3777,104 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3963,42 +3963,42 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,59 +4008,59 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4139,62 +4139,62 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4263,22 +4263,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4325,22 +4325,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4387,17 +4387,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4449,22 +4449,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4479,17 +4479,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,24 +4504,24 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4573,109 +4573,109 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4697,52 +4697,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4759,57 +4759,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4831,37 +4831,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,57 +4883,57 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5131,57 +5131,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5379,57 +5379,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,57 +5441,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,52 +5503,52 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5565,52 +5565,52 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5627,57 +5627,57 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5999,47 +5999,47 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>FORTENZA 600 FS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>600 g/l Cyantraniliprole</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ERİK KOŞNİLİ</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sphaerolecanium prunastri</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>22.5 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>MRL uygulanmaz.</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6049,72 +6049,10 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>FORTENZA 600 FS</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>FS</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>600 g/l Cyantraniliprole</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>PATATES</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Telkurtları</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Agriotes spp.</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>28 gün</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>22.5 ml/100 kg tohum</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
         <is>
           <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,22 +543,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,14 +660,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -677,37 +677,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -717,59 +717,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -791,17 +791,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SCORE 250 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Difenoconazole</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10 ml / 100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -863,47 +863,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -915,57 +915,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -977,57 +977,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,17 +1039,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1146,59 +1146,59 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1208,34 +1208,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1287,42 +1287,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1349,42 +1349,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1674,27 +1674,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1709,44 +1709,44 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1756,44 +1756,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2051,27 +2051,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2093,17 +2093,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,22 +2170,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2356,22 +2356,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2403,17 +2403,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2423,27 +2423,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2465,47 +2465,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2733,17 +2733,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,27 +2790,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2857,22 +2857,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2914,22 +2914,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3023,17 +3023,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,27 +3043,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3085,17 +3085,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3105,27 +3105,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3271,17 +3271,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3291,27 +3291,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,47 +3333,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,17 +3395,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3415,27 +3415,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3457,17 +3457,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3643,52 +3643,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3705,32 +3705,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3767,57 +3767,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,47 +3829,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3884,59 +3884,59 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
@@ -3973,12 +3973,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4077,32 +4077,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4112,84 +4112,84 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4201,62 +4201,62 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4325,22 +4325,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4360,12 +4360,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4387,22 +4387,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4449,17 +4449,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4511,22 +4511,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4566,24 +4566,24 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4635,32 +4635,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,34 +4670,34 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4707,37 +4707,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4759,57 +4759,57 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,57 +4821,57 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4893,37 +4893,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5131,57 +5131,57 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5441,57 +5441,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,57 +5503,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,52 +5565,52 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5627,52 +5627,52 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5689,74 +5689,74 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5766,32 +5766,32 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5801,29 +5801,29 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5875,47 +5875,47 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>50 ml/100 L su</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5937,57 +5937,57 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HAŞHAŞ </t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Haşhaş mildiyösü</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Peronospora arborescens</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>40-105 ml/da</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5999,62 +5999,62 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FORTENZA 600 FS</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>600 g/l Cyantraniliprole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Haşhaş mildiyösü</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Peronospora arborescens</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>22.5 ml/100 kg tohum</t>
+          <t>40-105 ml/da</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Afyonkarahisar ili için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,47 +543,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 - 100 ml/ 1 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen bitkilere uygulanmalıdır, gıda olarak yetiştiriciliği yapılan bitkilere uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -660,29 +660,29 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -722,14 +722,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -739,37 +739,37 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -791,47 +791,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SCORE 250 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>250 g/l Difenoconazole</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10 ml / 100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,69 +965,69 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,32 +1039,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1163,104 +1163,104 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1287,17 +1287,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1349,42 +1349,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1411,42 +1411,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1721,94 +1721,94 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1818,22 +1818,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,52 +1845,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1907,52 +1907,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1969,47 +1969,47 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2019,59 +2019,59 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2081,59 +2081,59 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,183 +2143,183 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2403,47 +2403,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,17 +2480,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2589,47 +2589,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2790,32 +2790,32 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2914,17 +2914,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2961,47 +2961,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,47 +3023,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,47 +3271,47 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,47 +3395,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,17 +3534,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3581,47 +3581,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3643,52 +3643,52 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3705,52 +3705,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3767,32 +3767,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,32 +3829,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3864,136 +3864,136 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4003,59 +4003,59 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4065,59 +4065,59 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,64 +4127,64 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4201,57 +4201,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4707,37 +4707,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Gülde karaleke</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Diplocarpon rosae</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4814,59 +4814,59 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>CELEST MAX 100 FS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Fludioxonil</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kök çürüklüğü hastalığı</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>10 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0.05* mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4893,37 +4893,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KİMYON</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GÜL PASI</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Phragmidium mucronatum</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100 ml/ 100 l su</t>
+          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4945,57 +4945,57 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Kurşuni küf</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Botrytis cinerea</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>80 g/100 l su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5007,57 +5007,57 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Gülde karaleke</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Diplocarpon rosae</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5193,57 +5193,57 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>GÜL (Süs bitkisi)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>GÜL PASI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Phragmidium mucronatum</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>100 ml/ 100 l su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>Azoxystrobin:60 mg/kg, Difenoconazole:20 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,005</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5441,57 +5441,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>66 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,57 +5503,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ANASON</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Anason yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cercospora malkoffii</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>60 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,52 +5565,52 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CELEST MAX 100 FS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>100 g/l Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kök çürüklüğü hastalığı</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Macrophomina phaseolina, Fusarium oxysporium</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>10 ml/100 kg tohuma</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.05* mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5627,52 +5627,52 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KİMYON</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>112,5 (yüz on iki buçuk) ml/dekar</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5689,57 +5689,57 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GÜL (Süs bitkisi)</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kurşuni küf</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Botrytis cinerea</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>80 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Cyprodinil:0.1* Fludioxonil:0,05*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5751,119 +5751,119 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>66 ml/100 kg tohuma</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>ANASON</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Anason yaprak lekesi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Cercospora malkoffii</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>60 ml/da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,47 +5875,47 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AVOKADO</t>
+          <t>KANOLA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>İncir Teke Böceği</t>
+          <t>Lahana yaprakgüvesi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Batocera rufomaculata</t>
+          <t>Plutella xylostella = Plutella maculipennis</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>50 ml/100 L su</t>
+          <t>100 ml/da</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5952,32 +5952,32 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KANOLA</t>
+          <t>AVOKADO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lahana yaprakgüvesi</t>
+          <t>İncir Teke Böceği</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Plutella xylostella = Plutella maculipennis</t>
+          <t>Batocera rufomaculata</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>100 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5999,60 +5999,122 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>AMPLİGO 150 ZC</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AVOKADO</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>İncir Teke Böceği</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Batocera rufomaculata</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>14 Gün</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>50 ml/100 L su</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Chlorantraniliprole: 0,3 Lambda-cyhalothrin:0,15</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>QUADRİS</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t xml:space="preserve">HAŞHAŞ </t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Haşhaş mildiyösü</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Peronospora arborescens</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>35 gün</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>40-105 ml/da</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>0.5 mg/kg</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Fungisit</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50 - 100 ml/ 1 L su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen bitkilere uygulanmalıdır, gıda olarak yetiştiriciliği yapılan bitkilere uygulanmamalıdır.</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,32 +543,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -593,59 +593,59 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,59 +655,59 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -717,59 +717,59 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -779,59 +779,59 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,44 +841,44 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -903,44 +903,44 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -965,19 +965,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SCORE 250 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -987,146 +987,146 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Difenoconazole</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10 ml / 100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1146,24 +1146,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1173,37 +1173,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1213,44 +1213,44 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1275,54 +1275,54 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1332,126 +1332,126 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1473,47 +1473,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1523,59 +1523,59 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1585,54 +1585,54 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1674,27 +1674,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1709,121 +1709,121 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SCORE 250 EC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>10 ml / 100 L su</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Cyprodinil:1 Lambda cyhalothrin:0,15</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,32 +1845,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1907,57 +1907,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1969,7 +1969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1979,37 +1979,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2019,81 +2019,81 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-30</t>
         </i